--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ106"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9302,10 +9302,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>98765518</v>
+        <v>136650666</v>
       </c>
       <c r="B76" t="n">
-        <v>58327</v>
+        <v>58003</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9313,16 +9313,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9335,15 +9335,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9352,10 +9346,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>654794</v>
+        <v>654896</v>
       </c>
       <c r="R76" t="n">
-        <v>6626077</v>
+        <v>6626428</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9382,22 +9376,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9423,33 +9417,33 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98765518</t>
+          <t>https://artportalen.se/Sighting/136650666</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>98677366</v>
+        <v>98765518</v>
       </c>
       <c r="B77" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9459,7 +9453,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9470,7 +9464,7 @@
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9479,10 +9473,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655016</v>
+        <v>654794</v>
       </c>
       <c r="R77" t="n">
-        <v>6626045</v>
+        <v>6626077</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9509,22 +9503,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9550,59 +9544,69 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98677366</t>
+          <t>https://artportalen.se/Sighting/98765518</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128316297</v>
+        <v>98677366</v>
       </c>
       <c r="B78" t="n">
-        <v>8455</v>
+        <v>58112</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>103020</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>654873</v>
+        <v>655016</v>
       </c>
       <c r="R78" t="n">
-        <v>6626177</v>
+        <v>6626045</v>
       </c>
       <c r="S78" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9626,12 +9630,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-19</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-19</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9640,83 +9654,76 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316297</t>
+          <t>https://artportalen.se/Sighting/98677366</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>96053393</v>
+        <v>128316297</v>
       </c>
       <c r="B79" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654985</v>
+        <v>654873</v>
       </c>
       <c r="R79" t="n">
-        <v>6626101</v>
+        <v>6626177</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9740,22 +9747,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:31</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:31</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9764,30 +9761,31 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96053393</t>
+          <t>https://artportalen.se/Sighting/128316297</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>98607855</v>
+        <v>96053393</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9817,7 +9815,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9829,14 +9827,14 @@
       <c r="L80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654901</v>
+        <v>654985</v>
       </c>
       <c r="R80" t="n">
-        <v>6626274</v>
+        <v>6626101</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9863,22 +9861,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9893,24 +9891,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98607855</t>
+          <t>https://artportalen.se/Sighting/96053393</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>98608115</v>
+        <v>98607855</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9938,7 +9936,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
@@ -9947,10 +9954,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654843</v>
+        <v>654901</v>
       </c>
       <c r="R81" t="n">
-        <v>6626288</v>
+        <v>6626274</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9982,7 +9989,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9992,7 +9999,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10018,13 +10025,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608115</t>
+          <t>https://artportalen.se/Sighting/98607855</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98608409</v>
+        <v>98608115</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -10052,16 +10059,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
@@ -10070,10 +10068,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>654854</v>
+        <v>654843</v>
       </c>
       <c r="R82" t="n">
-        <v>6626301</v>
+        <v>6626288</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10105,7 +10103,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10115,7 +10113,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10141,13 +10139,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608409</t>
+          <t>https://artportalen.se/Sighting/98608115</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>98608502</v>
+        <v>98608409</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10177,7 +10175,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10193,10 +10191,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654919</v>
+        <v>654854</v>
       </c>
       <c r="R83" t="n">
-        <v>6626271</v>
+        <v>6626301</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10228,7 +10226,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10238,7 +10236,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10264,13 +10262,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608502</t>
+          <t>https://artportalen.se/Sighting/98608409</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>99035628</v>
+        <v>98608502</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -10305,14 +10303,10 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10323,7 +10317,7 @@
         <v>654919</v>
       </c>
       <c r="R84" t="n">
-        <v>6626274</v>
+        <v>6626271</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10350,22 +10344,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10391,13 +10385,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99035628</t>
+          <t>https://artportalen.se/Sighting/98608502</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>99250188</v>
+        <v>99035628</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -10427,7 +10421,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10435,7 +10429,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10443,13 +10441,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654914</v>
+        <v>654919</v>
       </c>
       <c r="R85" t="n">
-        <v>6626178</v>
+        <v>6626274</v>
       </c>
       <c r="S85" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10473,22 +10471,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10514,13 +10512,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99250188</t>
+          <t>https://artportalen.se/Sighting/99035628</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>99298343</v>
+        <v>99250188</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -10566,13 +10564,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654976</v>
+        <v>654914</v>
       </c>
       <c r="R86" t="n">
-        <v>6626119</v>
+        <v>6626178</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10596,22 +10594,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10637,13 +10635,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99298343</t>
+          <t>https://artportalen.se/Sighting/99250188</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>100191450</v>
+        <v>99298343</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -10671,7 +10669,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
@@ -10680,10 +10687,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654885</v>
+        <v>654976</v>
       </c>
       <c r="R87" t="n">
-        <v>6626320</v>
+        <v>6626119</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -10710,22 +10717,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10751,13 +10758,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100191450</t>
+          <t>https://artportalen.se/Sighting/99298343</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>100384691</v>
+        <v>100191450</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -10794,10 +10801,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654875</v>
+        <v>654885</v>
       </c>
       <c r="R88" t="n">
-        <v>6626261</v>
+        <v>6626320</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -10824,22 +10831,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10865,13 +10872,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100384691</t>
+          <t>https://artportalen.se/Sighting/100191450</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>104297499</v>
+        <v>100384691</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -10899,27 +10906,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>654801</v>
+        <v>654875</v>
       </c>
       <c r="R89" t="n">
-        <v>6626326</v>
+        <v>6626261</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -10946,22 +10945,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10987,13 +10986,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297499</t>
+          <t>https://artportalen.se/Sighting/100384691</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>106211456</v>
+        <v>104297499</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -11023,20 +11022,25 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tagstahammaren, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>654947</v>
+        <v>654801</v>
       </c>
       <c r="R90" t="n">
-        <v>6626192</v>
+        <v>6626326</v>
       </c>
       <c r="S90" t="n">
         <v>25</v>
@@ -11063,22 +11067,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11104,13 +11108,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106211456</t>
+          <t>https://artportalen.se/Sighting/104297499</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>108944701</v>
+        <v>106211456</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11140,29 +11144,20 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>654877</v>
+        <v>654947</v>
       </c>
       <c r="R91" t="n">
-        <v>6626241</v>
+        <v>6626192</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -11189,22 +11184,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11230,13 +11225,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108944701</t>
+          <t>https://artportalen.se/Sighting/106211456</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112249551</v>
+        <v>108944701</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -11266,7 +11261,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11281,17 +11276,17 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>654785</v>
+        <v>654877</v>
       </c>
       <c r="R92" t="n">
-        <v>6626333</v>
+        <v>6626241</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11315,22 +11310,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11341,11 +11336,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -11361,13 +11351,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112249551</t>
+          <t>https://artportalen.se/Sighting/108944701</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112251982</v>
+        <v>112249551</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -11397,25 +11387,29 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>654747</v>
+        <v>654785</v>
       </c>
       <c r="R93" t="n">
-        <v>6626129</v>
+        <v>6626333</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11447,7 +11441,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11457,7 +11451,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11468,6 +11462,11 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11483,56 +11482,64 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112251982</t>
+          <t>https://artportalen.se/Sighting/112249551</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>98609287</v>
+        <v>112251982</v>
       </c>
       <c r="B94" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>654998</v>
+        <v>654747</v>
       </c>
       <c r="R94" t="n">
-        <v>6626133</v>
+        <v>6626129</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11556,22 +11563,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11597,13 +11604,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609287</t>
+          <t>https://artportalen.se/Sighting/112251982</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>98642582</v>
+        <v>98609287</v>
       </c>
       <c r="B95" t="n">
         <v>101326</v>
@@ -11631,16 +11638,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11649,10 +11647,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654896</v>
+        <v>654998</v>
       </c>
       <c r="R95" t="n">
-        <v>6626428</v>
+        <v>6626133</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11679,22 +11677,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11720,16 +11718,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98642582</t>
+          <t>https://artportalen.se/Sighting/98609287</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132632842</v>
+        <v>98642582</v>
       </c>
       <c r="B96" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11756,7 +11754,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11764,21 +11762,18 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654863</v>
+        <v>654896</v>
       </c>
       <c r="R96" t="n">
-        <v>6626472</v>
+        <v>6626428</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11805,22 +11800,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11831,11 +11826,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11851,16 +11841,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132632842</t>
+          <t>https://artportalen.se/Sighting/98642582</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>104297588</v>
+        <v>132632842</v>
       </c>
       <c r="B97" t="n">
-        <v>101228</v>
+        <v>101403</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11868,39 +11858,48 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>654786</v>
+        <v>654863</v>
       </c>
       <c r="R97" t="n">
-        <v>6626345</v>
+        <v>6626472</v>
       </c>
       <c r="S97" t="n">
         <v>25</v>
@@ -11927,22 +11926,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11953,6 +11952,11 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -11968,13 +11972,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297588</t>
+          <t>https://artportalen.se/Sighting/132632842</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112090750</v>
+        <v>104297588</v>
       </c>
       <c r="B98" t="n">
         <v>101228</v>
@@ -12007,29 +12011,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>654798</v>
+        <v>654786</v>
       </c>
       <c r="R98" t="n">
-        <v>6626355</v>
+        <v>6626345</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12053,22 +12048,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12094,16 +12089,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112090750</t>
+          <t>https://artportalen.se/Sighting/104297588</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98609195</v>
+        <v>112090750</v>
       </c>
       <c r="B99" t="n">
-        <v>99038</v>
+        <v>101228</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12111,22 +12106,26 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>223597</v>
+        <v>222771</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12136,23 +12135,22 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>654998</v>
+        <v>654798</v>
       </c>
       <c r="R99" t="n">
-        <v>6626133</v>
+        <v>6626355</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12176,12 +12174,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12207,52 +12215,62 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609195</t>
+          <t>https://artportalen.se/Sighting/112090750</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>96054296</v>
+        <v>98609195</v>
       </c>
       <c r="B100" t="n">
-        <v>93194</v>
+        <v>99038</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>239737</v>
+        <v>223597</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>654742</v>
+        <v>654998</v>
       </c>
       <c r="R100" t="n">
-        <v>6626141</v>
+        <v>6626133</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12279,22 +12297,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:07</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12309,24 +12317,24 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96054296</t>
+          <t>https://artportalen.se/Sighting/98609195</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100501116</v>
+        <v>96054296</v>
       </c>
       <c r="B101" t="n">
         <v>93194</v>
@@ -12354,31 +12362,21 @@
           <t>K.A.Harrison</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Tagsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>654735</v>
+        <v>654742</v>
       </c>
       <c r="R101" t="n">
-        <v>6626144</v>
+        <v>6626141</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12402,17 +12400,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Fjolårsexemplar</t>
+          <t>2021-09-12</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12421,36 +12424,30 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Intill sten på stig</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100501116</t>
+          <t>https://artportalen.se/Sighting/96054296</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>112265989</v>
+        <v>100501116</v>
       </c>
       <c r="B102" t="n">
         <v>93194</v>
@@ -12480,7 +12477,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12489,16 +12486,17 @@
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Tagsta, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>654747</v>
+        <v>654735</v>
       </c>
       <c r="R102" t="n">
-        <v>6626129</v>
+        <v>6626144</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12525,22 +12523,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12549,35 +12542,36 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Intill sten på stig</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112265989</t>
+          <t>https://artportalen.se/Sighting/100501116</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112266023</v>
+        <v>112265989</v>
       </c>
       <c r="B103" t="n">
         <v>93194</v>
@@ -12618,14 +12612,14 @@
       <c r="K103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>654744</v>
+        <v>654747</v>
       </c>
       <c r="R103" t="n">
-        <v>6626117</v>
+        <v>6626129</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -12657,7 +12651,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12667,7 +12661,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12678,6 +12672,11 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -12693,13 +12692,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112266023</t>
+          <t>https://artportalen.se/Sighting/112265989</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112267670</v>
+        <v>112266023</v>
       </c>
       <c r="B104" t="n">
         <v>93194</v>
@@ -12727,7 +12726,16 @@
           <t>K.A.Harrison</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12735,10 +12743,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654750</v>
+        <v>654744</v>
       </c>
       <c r="R104" t="n">
-        <v>6626105</v>
+        <v>6626117</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12770,7 +12778,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12780,7 +12788,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12806,59 +12814,55 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112267670</t>
+          <t>https://artportalen.se/Sighting/112266023</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>98936021</v>
+        <v>112267670</v>
       </c>
       <c r="B105" t="n">
-        <v>92329</v>
+        <v>93194</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6040186</v>
+        <v>239737</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>654936</v>
+        <v>654750</v>
       </c>
       <c r="R105" t="n">
-        <v>6626103</v>
+        <v>6626105</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12882,22 +12886,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12912,24 +12916,24 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98936021</t>
+          <t>https://artportalen.se/Sighting/112267670</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>104259921</v>
+        <v>98936021</v>
       </c>
       <c r="B106" t="n">
         <v>92329</v>
@@ -12957,7 +12961,11 @@
           <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12965,10 +12973,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>654969</v>
+        <v>654936</v>
       </c>
       <c r="R106" t="n">
-        <v>6626078</v>
+        <v>6626103</v>
       </c>
       <c r="S106" t="n">
         <v>25</v>
@@ -12995,22 +13003,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13025,16 +13033,129 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Elisabet Ottosson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936021</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>104259921</v>
+      </c>
+      <c r="B107" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>654969</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6626078</v>
+      </c>
+      <c r="S107" t="n">
+        <v>25</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104259921</t>
         </is>
@@ -13147,6 +13268,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92336</v>
+        <v>92338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136799374</v>
       </c>
       <c r="B74" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136799373</v>
       </c>
       <c r="B106" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136799375</v>
       </c>
       <c r="B118" t="n">
-        <v>92502</v>
+        <v>92504</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136799374</v>
       </c>
       <c r="B74" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136799373</v>
       </c>
       <c r="B106" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136799375</v>
       </c>
       <c r="B118" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136799374</v>
       </c>
       <c r="B74" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136799373</v>
       </c>
       <c r="B106" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136799375</v>
       </c>
       <c r="B118" t="n">
-        <v>92506</v>
+        <v>92508</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>136799374</v>
       </c>
       <c r="B74" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>136799373</v>
       </c>
       <c r="B106" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136799375</v>
       </c>
       <c r="B118" t="n">
-        <v>92508</v>
+        <v>92509</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ120"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8420,51 +8420,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128316251</v>
+        <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>91282</v>
+        <v>92139</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5685</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654871</v>
+        <v>654835</v>
       </c>
       <c r="R69" t="n">
-        <v>6626148</v>
+        <v>6626150</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8488,12 +8485,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Två ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8502,56 +8514,45 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Carin von Köhler</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
-        </is>
-      </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316251</t>
+          <t>https://artportalen.se/Sighting/137123350</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128316139</v>
+        <v>128316251</v>
       </c>
       <c r="B70" t="n">
-        <v>91424</v>
+        <v>91282</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5733</v>
+        <v>5685</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8560,14 +8561,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>tagstaskogen, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>654757</v>
+        <v>654871</v>
       </c>
       <c r="R70" t="n">
-        <v>6626122</v>
+        <v>6626148</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8626,55 +8627,57 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316139</t>
+          <t>https://artportalen.se/Sighting/128316251</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96053454</v>
+        <v>128316139</v>
       </c>
       <c r="B71" t="n">
-        <v>92567</v>
+        <v>91424</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6031</v>
+        <v>5733</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>654866</v>
+        <v>654757</v>
       </c>
       <c r="R71" t="n">
-        <v>6626210</v>
+        <v>6626122</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8698,22 +8701,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:12</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8722,30 +8715,31 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96053454</t>
+          <t>https://artportalen.se/Sighting/128316139</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>98632141</v>
+        <v>96053454</v>
       </c>
       <c r="B72" t="n">
         <v>92567</v>
@@ -8773,22 +8767,18 @@
           <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>654821</v>
+        <v>654866</v>
       </c>
       <c r="R72" t="n">
-        <v>6626087</v>
+        <v>6626210</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8815,22 +8805,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-02-15</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8845,24 +8835,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hans Bärring</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hans Bärring</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98632141</t>
+          <t>https://artportalen.se/Sighting/96053454</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128316450</v>
+        <v>98632141</v>
       </c>
       <c r="B73" t="n">
         <v>92567</v>
@@ -8890,23 +8880,25 @@
           <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>654938</v>
+        <v>654821</v>
       </c>
       <c r="R73" t="n">
-        <v>6626130</v>
+        <v>6626087</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8930,12 +8922,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8944,34 +8946,33 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Hans Bärring</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Hans Bärring</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316450</t>
+          <t>https://artportalen.se/Sighting/98632141</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136799374</v>
+        <v>128316450</v>
       </c>
       <c r="B74" t="n">
-        <v>92796</v>
+        <v>92567</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8997,19 +8998,22 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654861</v>
+        <v>654938</v>
       </c>
       <c r="R74" t="n">
-        <v>6626210</v>
+        <v>6626130</v>
       </c>
       <c r="S74" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9033,22 +9037,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9057,33 +9051,34 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799374</t>
+          <t>https://artportalen.se/Sighting/128316450</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>100400258</v>
+        <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>57247</v>
+        <v>92796</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,49 +9086,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100038</v>
+        <v>6031</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Tagsta Ö, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>655110</v>
+        <v>654861</v>
       </c>
       <c r="R75" t="n">
-        <v>6626111</v>
+        <v>6626210</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9157,27 +9140,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2022-04-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2022-04-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Två skogsduvor satt lugnt och länge tillsammans i större lövträd. Ca 11.20 hördes den karaktäristiska sången. Lämpligt större bohål finns ca 50 m från obsplatsen.</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9192,24 +9170,24 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100400258</t>
+          <t>https://artportalen.se/Sighting/136799374</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>109511138</v>
+        <v>100400258</v>
       </c>
       <c r="B76" t="n">
         <v>57247</v>
@@ -9239,7 +9217,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9247,26 +9225,19 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Tagstahammaren, Upl</t>
+          <t>Tagsta Ö, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>655067</v>
+        <v>655110</v>
       </c>
       <c r="R76" t="n">
-        <v>6626105</v>
+        <v>6626111</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9293,22 +9264,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2022-04-30</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Två skogsduvor satt lugnt och länge tillsammans i större lövträd. Ca 11.20 hördes den karaktäristiska sången. Lämpligt större bohål finns ca 50 m från obsplatsen.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9334,13 +9310,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109511138</t>
+          <t>https://artportalen.se/Sighting/100400258</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>109843058</v>
+        <v>109511138</v>
       </c>
       <c r="B77" t="n">
         <v>57247</v>
@@ -9385,7 +9361,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9394,10 +9370,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>655075</v>
+        <v>655067</v>
       </c>
       <c r="R77" t="n">
-        <v>6626126</v>
+        <v>6626105</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9424,22 +9400,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9465,54 +9441,73 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109843058</t>
+          <t>https://artportalen.se/Sighting/109511138</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>98639070</v>
+        <v>109843058</v>
       </c>
       <c r="B78" t="n">
-        <v>57966</v>
+        <v>57247</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sverige, Upl</t>
+          <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>654880</v>
+        <v>655075</v>
       </c>
       <c r="R78" t="n">
         <v>6626126</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9536,12 +9531,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2022-02-05</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9556,24 +9561,24 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98639070</t>
+          <t>https://artportalen.se/Sighting/109843058</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>98677381</v>
+        <v>98639070</v>
       </c>
       <c r="B79" t="n">
         <v>57966</v>
@@ -9601,35 +9606,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Sverige, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>655016</v>
+        <v>654880</v>
       </c>
       <c r="R79" t="n">
-        <v>6626045</v>
+        <v>6626126</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9653,22 +9643,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9683,24 +9663,24 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98677381</t>
+          <t>https://artportalen.se/Sighting/98639070</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>99297808</v>
+        <v>98677381</v>
       </c>
       <c r="B80" t="n">
         <v>57966</v>
@@ -9733,23 +9713,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Tagsta 526, Knivsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654819</v>
+        <v>655016</v>
       </c>
       <c r="R80" t="n">
-        <v>6626053</v>
+        <v>6626045</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9776,22 +9760,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9817,13 +9801,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99297808</t>
+          <t>https://artportalen.se/Sighting/98677381</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>100388318</v>
+        <v>99297808</v>
       </c>
       <c r="B81" t="n">
         <v>57966</v>
@@ -9856,16 +9840,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -9873,14 +9849,14 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagsta 526, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>655009</v>
+        <v>654819</v>
       </c>
       <c r="R81" t="n">
-        <v>6626092</v>
+        <v>6626053</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -9907,22 +9883,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9948,33 +9924,33 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100388318</t>
+          <t>https://artportalen.se/Sighting/99297808</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>98804218</v>
+        <v>100388318</v>
       </c>
       <c r="B82" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9987,11 +9963,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10003,7 +9987,7 @@
         <v>655009</v>
       </c>
       <c r="R82" t="n">
-        <v>6626137</v>
+        <v>6626092</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10030,22 +10014,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2022-02-27</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10071,16 +10055,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98804218</t>
+          <t>https://artportalen.se/Sighting/100388318</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135987246</v>
+        <v>98804218</v>
       </c>
       <c r="B83" t="n">
-        <v>58003</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10110,6 +10094,8 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -10121,10 +10107,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654915</v>
+        <v>655009</v>
       </c>
       <c r="R83" t="n">
-        <v>6626038</v>
+        <v>6626137</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10151,22 +10137,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2022-02-27</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10192,16 +10178,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135987246</t>
+          <t>https://artportalen.se/Sighting/98804218</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136650666</v>
+        <v>135987246</v>
       </c>
       <c r="B84" t="n">
-        <v>58005</v>
+        <v>58003</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10242,10 +10228,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654896</v>
+        <v>654915</v>
       </c>
       <c r="R84" t="n">
-        <v>6626428</v>
+        <v>6626038</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10272,22 +10258,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10313,13 +10299,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136650666</t>
+          <t>https://artportalen.se/Sighting/135987246</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136799364</v>
+        <v>136650666</v>
       </c>
       <c r="B85" t="n">
         <v>58005</v>
@@ -10347,20 +10333,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654803</v>
+        <v>654896</v>
       </c>
       <c r="R85" t="n">
-        <v>6626254</v>
+        <v>6626428</v>
       </c>
       <c r="S85" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10384,27 +10379,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10419,24 +10409,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799364</t>
+          <t>https://artportalen.se/Sighting/136650666</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136799369</v>
+        <v>136799364</v>
       </c>
       <c r="B86" t="n">
         <v>58005</v>
@@ -10471,13 +10461,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654763</v>
+        <v>654803</v>
       </c>
       <c r="R86" t="n">
-        <v>6626303</v>
+        <v>6626254</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10506,7 +10496,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10516,7 +10506,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -10547,16 +10537,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799369</t>
+          <t>https://artportalen.se/Sighting/136799364</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136799368</v>
+        <v>136799369</v>
       </c>
       <c r="B87" t="n">
-        <v>5182</v>
+        <v>58005</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10564,21 +10554,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10588,13 +10578,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654764</v>
+        <v>654763</v>
       </c>
       <c r="R87" t="n">
-        <v>6626304</v>
+        <v>6626303</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10623,7 +10613,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10633,7 +10623,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10659,16 +10654,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799368</t>
+          <t>https://artportalen.se/Sighting/136799369</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>98765518</v>
+        <v>137123346</v>
       </c>
       <c r="B88" t="n">
-        <v>58327</v>
+        <v>58005</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10676,16 +10671,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10693,35 +10688,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654794</v>
+        <v>654827</v>
       </c>
       <c r="R88" t="n">
-        <v>6626077</v>
+        <v>6626180</v>
       </c>
       <c r="S88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10745,22 +10729,27 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-02-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska spår efter födosök (hack i träd)</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10773,82 +10762,57 @@
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Marie Kvarnström</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Marie Kvarnström</t>
-        </is>
-      </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98765518</t>
+          <t>https://artportalen.se/Sighting/137123346</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98677366</v>
+        <v>136799368</v>
       </c>
       <c r="B89" t="n">
-        <v>58112</v>
+        <v>5182</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103020</v>
+        <v>100526</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>655016</v>
+        <v>654764</v>
       </c>
       <c r="R89" t="n">
-        <v>6626045</v>
+        <v>6626304</v>
       </c>
       <c r="S89" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10872,22 +10836,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10902,27 +10866,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98677366</t>
+          <t>https://artportalen.se/Sighting/136799368</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128316297</v>
+        <v>98765518</v>
       </c>
       <c r="B90" t="n">
-        <v>8455</v>
+        <v>58327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10930,42 +10894,52 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>654873</v>
+        <v>654794</v>
       </c>
       <c r="R90" t="n">
-        <v>6626177</v>
+        <v>6626077</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10989,12 +10963,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11003,56 +10987,55 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carin von Köhler, Marie Kvarnström</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128316297</t>
+          <t>https://artportalen.se/Sighting/98765518</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>96053393</v>
+        <v>98677366</v>
       </c>
       <c r="B91" t="n">
-        <v>99118</v>
+        <v>58112</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>103020</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11060,23 +11043,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>654985</v>
+        <v>655016</v>
       </c>
       <c r="R91" t="n">
-        <v>6626101</v>
+        <v>6626045</v>
       </c>
       <c r="S91" t="n">
         <v>25</v>
@@ -11103,22 +11090,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11133,76 +11120,70 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96053393</t>
+          <t>https://artportalen.se/Sighting/98677366</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>98607855</v>
+        <v>128316297</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>654901</v>
+        <v>654873</v>
       </c>
       <c r="R92" t="n">
-        <v>6626274</v>
+        <v>6626177</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11226,22 +11207,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>13:57</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11250,30 +11221,31 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Carin von Köhler, Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98607855</t>
+          <t>https://artportalen.se/Sighting/128316297</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>98608115</v>
+        <v>96053393</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -11301,19 +11273,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>654843</v>
+        <v>654985</v>
       </c>
       <c r="R93" t="n">
-        <v>6626288</v>
+        <v>6626101</v>
       </c>
       <c r="S93" t="n">
         <v>25</v>
@@ -11340,22 +11321,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11370,24 +11351,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608115</t>
+          <t>https://artportalen.se/Sighting/96053393</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>98608409</v>
+        <v>98607855</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -11417,12 +11398,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -11433,10 +11414,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>654854</v>
+        <v>654901</v>
       </c>
       <c r="R94" t="n">
-        <v>6626301</v>
+        <v>6626274</v>
       </c>
       <c r="S94" t="n">
         <v>25</v>
@@ -11468,7 +11449,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11478,7 +11459,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11504,13 +11485,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608409</t>
+          <t>https://artportalen.se/Sighting/98607855</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>98608502</v>
+        <v>98608115</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -11538,16 +11519,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11556,10 +11528,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654919</v>
+        <v>654843</v>
       </c>
       <c r="R95" t="n">
-        <v>6626271</v>
+        <v>6626288</v>
       </c>
       <c r="S95" t="n">
         <v>25</v>
@@ -11591,7 +11563,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11601,7 +11573,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11627,13 +11599,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98608502</t>
+          <t>https://artportalen.se/Sighting/98608115</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>99035628</v>
+        <v>98608409</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -11663,19 +11635,15 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11683,10 +11651,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654919</v>
+        <v>654854</v>
       </c>
       <c r="R96" t="n">
-        <v>6626274</v>
+        <v>6626301</v>
       </c>
       <c r="S96" t="n">
         <v>25</v>
@@ -11713,22 +11681,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2022-03-11</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11754,13 +11722,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99035628</t>
+          <t>https://artportalen.se/Sighting/98608409</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>99250188</v>
+        <v>98608502</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -11790,12 +11758,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -11806,13 +11774,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>654914</v>
+        <v>654919</v>
       </c>
       <c r="R97" t="n">
-        <v>6626178</v>
+        <v>6626271</v>
       </c>
       <c r="S97" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11836,22 +11804,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2022-03-19</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11877,13 +11845,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99250188</t>
+          <t>https://artportalen.se/Sighting/98608502</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>99298343</v>
+        <v>99035628</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -11913,7 +11881,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11921,7 +11889,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11929,10 +11901,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>654976</v>
+        <v>654919</v>
       </c>
       <c r="R98" t="n">
-        <v>6626119</v>
+        <v>6626274</v>
       </c>
       <c r="S98" t="n">
         <v>25</v>
@@ -11959,22 +11931,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12000,13 +11972,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99298343</t>
+          <t>https://artportalen.se/Sighting/99035628</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>100191450</v>
+        <v>99250188</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -12034,7 +12006,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -12043,13 +12024,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>654885</v>
+        <v>654914</v>
       </c>
       <c r="R99" t="n">
-        <v>6626320</v>
+        <v>6626178</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12073,22 +12054,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-03-19</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12114,13 +12095,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100191450</t>
+          <t>https://artportalen.se/Sighting/99250188</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>100384691</v>
+        <v>99298343</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -12148,7 +12129,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -12157,10 +12147,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>654875</v>
+        <v>654976</v>
       </c>
       <c r="R100" t="n">
-        <v>6626261</v>
+        <v>6626119</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12187,22 +12177,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12228,13 +12218,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100384691</t>
+          <t>https://artportalen.se/Sighting/99298343</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>104297499</v>
+        <v>100191450</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -12262,27 +12252,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>654801</v>
+        <v>654885</v>
       </c>
       <c r="R101" t="n">
-        <v>6626326</v>
+        <v>6626320</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -12309,22 +12291,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12350,13 +12332,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297499</t>
+          <t>https://artportalen.se/Sighting/100191450</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>106211456</v>
+        <v>100384691</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -12384,22 +12366,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Tagstahammaren, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>654947</v>
+        <v>654875</v>
       </c>
       <c r="R102" t="n">
-        <v>6626192</v>
+        <v>6626261</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12426,22 +12405,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12467,13 +12446,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106211456</t>
+          <t>https://artportalen.se/Sighting/100384691</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>108944701</v>
+        <v>104297499</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -12503,29 +12482,25 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Tagstahammaren, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>654877</v>
+        <v>654801</v>
       </c>
       <c r="R103" t="n">
-        <v>6626241</v>
+        <v>6626326</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12552,22 +12527,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12593,13 +12568,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108944701</t>
+          <t>https://artportalen.se/Sighting/104297499</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112249551</v>
+        <v>106211456</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -12629,32 +12604,23 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654785</v>
+        <v>654947</v>
       </c>
       <c r="R104" t="n">
-        <v>6626333</v>
+        <v>6626192</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12678,22 +12644,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-01-29</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12704,11 +12670,6 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -12724,13 +12685,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112249551</t>
+          <t>https://artportalen.se/Sighting/106211456</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>112251982</v>
+        <v>108944701</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -12760,28 +12721,32 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Tagstahammaren, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>654747</v>
+        <v>654877</v>
       </c>
       <c r="R105" t="n">
-        <v>6626129</v>
+        <v>6626241</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12805,22 +12770,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12846,16 +12811,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112251982</t>
+          <t>https://artportalen.se/Sighting/108944701</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136799373</v>
+        <v>112249551</v>
       </c>
       <c r="B106" t="n">
-        <v>99362</v>
+        <v>99118</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12880,17 +12845,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>654864</v>
+        <v>654785</v>
       </c>
       <c r="R106" t="n">
-        <v>6626205</v>
+        <v>6626333</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12917,22 +12896,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12943,71 +12922,84 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799373</t>
+          <t>https://artportalen.se/Sighting/112249551</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>98609287</v>
+        <v>112251982</v>
       </c>
       <c r="B107" t="n">
-        <v>101326</v>
+        <v>99118</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>654998</v>
+        <v>654747</v>
       </c>
       <c r="R107" t="n">
-        <v>6626133</v>
+        <v>6626129</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13031,22 +13023,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2022-02-13</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13072,65 +13064,54 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609287</t>
+          <t>https://artportalen.se/Sighting/112251982</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>98642582</v>
+        <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>101326</v>
+        <v>99362</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>654896</v>
+        <v>654864</v>
       </c>
       <c r="R108" t="n">
-        <v>6626428</v>
+        <v>6626205</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13154,22 +13135,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13184,76 +13165,67 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98642582</t>
+          <t>https://artportalen.se/Sighting/136799373</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132632842</v>
+        <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>101403</v>
+        <v>99362</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagsta, Upl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>654863</v>
+        <v>654906</v>
       </c>
       <c r="R109" t="n">
-        <v>6626472</v>
+        <v>6626256</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -13280,22 +13252,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13306,79 +13278,73 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Ylva Petersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132632842</t>
+          <t>https://artportalen.se/Sighting/136799616</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>104297588</v>
+        <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>101228</v>
+        <v>99362</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>654786</v>
+        <v>654882</v>
       </c>
       <c r="R110" t="n">
-        <v>6626345</v>
+        <v>6626263</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13402,22 +13368,27 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>"4 skott omelerade, ca 20 skott melerade blad</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13426,33 +13397,24 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Marie Kvarnström</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Marie Kvarnström</t>
-        </is>
-      </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104297588</t>
+          <t>https://artportalen.se/Sighting/137123349</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>112090750</v>
+        <v>98609287</v>
       </c>
       <c r="B111" t="n">
-        <v>101228</v>
+        <v>101326</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13460,51 +13422,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>654798</v>
+        <v>654998</v>
       </c>
       <c r="R111" t="n">
-        <v>6626355</v>
+        <v>6626133</v>
       </c>
       <c r="S111" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13528,22 +13478,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13569,16 +13519,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112090750</t>
+          <t>https://artportalen.se/Sighting/98609287</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>98609195</v>
+        <v>98642582</v>
       </c>
       <c r="B112" t="n">
-        <v>99038</v>
+        <v>101326</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13586,22 +13536,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -13609,11 +13563,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13621,10 +13571,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>654998</v>
+        <v>654896</v>
       </c>
       <c r="R112" t="n">
-        <v>6626133</v>
+        <v>6626428</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -13651,12 +13601,22 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2021-07-09</t>
+          <t>2022-02-16</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13682,52 +13642,65 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98609195</t>
+          <t>https://artportalen.se/Sighting/98642582</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>96054296</v>
+        <v>132632842</v>
       </c>
       <c r="B113" t="n">
-        <v>93194</v>
+        <v>101403</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>239737</v>
+        <v>222498</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>654742</v>
+        <v>654863</v>
       </c>
       <c r="R113" t="n">
-        <v>6626141</v>
+        <v>6626472</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -13754,22 +13727,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13780,80 +13753,79 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Karin Martinsson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96054296</t>
+          <t>https://artportalen.se/Sighting/132632842</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>100501116</v>
+        <v>104297588</v>
       </c>
       <c r="B114" t="n">
-        <v>93194</v>
+        <v>101228</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>239737</v>
+        <v>222771</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Tagsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>654735</v>
+        <v>654786</v>
       </c>
       <c r="R114" t="n">
-        <v>6626144</v>
+        <v>6626345</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13877,17 +13849,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-10-24</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Fjolårsexemplar</t>
+          <t>2022-10-24</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13896,87 +13873,85 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>Intill sten på stig</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Patrick Fritzson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100501116</t>
+          <t>https://artportalen.se/Sighting/104297588</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>112265989</v>
+        <v>112090750</v>
       </c>
       <c r="B115" t="n">
-        <v>93194</v>
+        <v>101228</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>239737</v>
+        <v>222771</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>K.A.Harrison</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>654747</v>
+        <v>654798</v>
       </c>
       <c r="R115" t="n">
-        <v>6626129</v>
+        <v>6626355</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14000,22 +13975,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14026,11 +14001,6 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -14046,64 +14016,65 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112265989</t>
+          <t>https://artportalen.se/Sighting/112090750</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112266023</v>
+        <v>98609195</v>
       </c>
       <c r="B116" t="n">
-        <v>93194</v>
+        <v>99038</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>239737</v>
+        <v>223597</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knölig taggsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum cumulatum</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>K.A.Harrison</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>654744</v>
+        <v>654998</v>
       </c>
       <c r="R116" t="n">
-        <v>6626117</v>
+        <v>6626133</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14127,22 +14098,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2021-07-09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14168,13 +14129,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112266023</t>
+          <t>https://artportalen.se/Sighting/98609195</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112267670</v>
+        <v>96054296</v>
       </c>
       <c r="B117" t="n">
         <v>93194</v>
@@ -14206,17 +14167,17 @@
       <c r="K117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Knivsta, Knivsta, Upl</t>
+          <t>Tagstaskogen, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>654750</v>
+        <v>654742</v>
       </c>
       <c r="R117" t="n">
-        <v>6626105</v>
+        <v>6626141</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14240,22 +14201,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14270,62 +14231,73 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Marie Kvarnström</t>
+          <t>Karin Martinsson, Ulf Swenson, Marie Kvarnström, Tomas Hallingbäck</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112267670</t>
+          <t>https://artportalen.se/Sighting/96054296</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136799375</v>
+        <v>100501116</v>
       </c>
       <c r="B118" t="n">
-        <v>92509</v>
+        <v>93194</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6040162</v>
+        <v>239737</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Tagstaskogen, Upl</t>
+          <t>Tagsta, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>654871</v>
+        <v>654735</v>
       </c>
       <c r="R118" t="n">
-        <v>6626236</v>
+        <v>6626144</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14352,22 +14324,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Fjolårsexemplar</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14376,76 +14343,87 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>Intill sten på stig</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Björn Bråvander, Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136799375</t>
+          <t>https://artportalen.se/Sighting/100501116</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>98936021</v>
+        <v>112265989</v>
       </c>
       <c r="B119" t="n">
-        <v>92329</v>
+        <v>93194</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6040186</v>
+        <v>239737</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>K.A.Harrison</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Tagstahammaren, nära kärret, Tagstahammaren, nära kärret, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>654936</v>
+        <v>654747</v>
       </c>
       <c r="R119" t="n">
-        <v>6626103</v>
+        <v>6626129</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14469,22 +14447,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14495,70 +14473,84 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Elisabet Ottosson</t>
+          <t>Marie Kvarnström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98936021</t>
+          <t>https://artportalen.se/Sighting/112265989</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>104259921</v>
+        <v>112266023</v>
       </c>
       <c r="B120" t="n">
-        <v>92329</v>
+        <v>93194</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6040186</v>
+        <v>239737</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Knölig taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hydnellum cumulatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Knivsta, Upl</t>
+          <t>Knivsta, Knivsta, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>654969</v>
+        <v>654744</v>
       </c>
       <c r="R120" t="n">
-        <v>6626078</v>
+        <v>6626117</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14582,22 +14574,22 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14622,6 +14614,675 @@
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112266023</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>112267670</v>
+      </c>
+      <c r="B121" t="n">
+        <v>93194</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>239737</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hydnellum cumulatum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>K.A.Harrison</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Knivsta, Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>654750</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6626105</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112267670</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>136799375</v>
+      </c>
+      <c r="B122" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>654871</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6626236</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799375</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>136799617</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Tagsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>654866</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6626243</v>
+      </c>
+      <c r="S123" t="n">
+        <v>20</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Ylva Petersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136799617</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>137123352</v>
+      </c>
+      <c r="B124" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Tagstaskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>654868</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6626250</v>
+      </c>
+      <c r="S124" t="n">
+        <v>6</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123352</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>98936021</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>654936</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6626103</v>
+      </c>
+      <c r="S125" t="n">
+        <v>25</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2022-03-06</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2022-03-06</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98936021</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>104259921</v>
+      </c>
+      <c r="B126" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Knivsta, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>654969</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6626078</v>
+      </c>
+      <c r="S126" t="n">
+        <v>25</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2022-10-22</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Marie Kvarnström</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104259921</t>
         </is>
@@ -14748,6 +15409,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8518,6 +8518,16 @@
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
@@ -9078,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10762,6 +10772,16 @@
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
@@ -13073,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13185,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13302,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13402,6 +13422,16 @@
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
@@ -14737,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92509</v>
+        <v>92515</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14849,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92509</v>
+        <v>92515</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14961,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92509</v>
+        <v>92515</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15051,6 +15081,16 @@
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Elin Deremar</t>
+        </is>
+      </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92515</v>
+        <v>92519</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92519</v>
+        <v>92521</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>136650666</v>
       </c>
       <c r="B85" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>136799364</v>
       </c>
       <c r="B86" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>136799369</v>
       </c>
       <c r="B87" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>137123346</v>
       </c>
       <c r="B88" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92521</v>
+        <v>92534</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92521</v>
+        <v>92534</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92521</v>
+        <v>92534</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>136650666</v>
       </c>
       <c r="B85" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>136799364</v>
       </c>
       <c r="B86" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>136799369</v>
       </c>
       <c r="B87" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>137123346</v>
       </c>
       <c r="B88" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92534</v>
+        <v>92536</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92536</v>
+        <v>92539</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>136799364</v>
       </c>
       <c r="B86" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>136799369</v>
       </c>
       <c r="B87" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>137123346</v>
       </c>
       <c r="B88" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>136799368</v>
       </c>
       <c r="B89" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92539</v>
+        <v>92549</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -3164,7 +3164,7 @@
         <v>136799365</v>
       </c>
       <c r="B24" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>136799363</v>
       </c>
       <c r="B41" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>136799366</v>
       </c>
       <c r="B42" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>136799370</v>
       </c>
       <c r="B43" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>136799367</v>
       </c>
       <c r="B56" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>136799362</v>
       </c>
       <c r="B67" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>136799372</v>
       </c>
       <c r="B68" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>137123350</v>
       </c>
       <c r="B69" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
         <v>136799374</v>
       </c>
       <c r="B75" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>136799373</v>
       </c>
       <c r="B108" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>136799616</v>
       </c>
       <c r="B109" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>137123349</v>
       </c>
       <c r="B110" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136799375</v>
       </c>
       <c r="B122" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136799617</v>
       </c>
       <c r="B123" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>137123352</v>
       </c>
       <c r="B124" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136799365</v>
       </c>
       <c r="B25" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>136799363</v>
       </c>
       <c r="B42" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>136799366</v>
       </c>
       <c r="B43" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>136799370</v>
       </c>
       <c r="B44" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>136799367</v>
       </c>
       <c r="B58" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>136799362</v>
       </c>
       <c r="B69" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>136799372</v>
       </c>
       <c r="B70" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136799374</v>
       </c>
       <c r="B79" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>136799364</v>
       </c>
       <c r="B90" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>136799369</v>
       </c>
       <c r="B91" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137123346</v>
       </c>
       <c r="B92" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>136799373</v>
       </c>
       <c r="B113" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136799375</v>
       </c>
       <c r="B129" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92550</v>
+        <v>92553</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136799365</v>
       </c>
       <c r="B25" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>136799363</v>
       </c>
       <c r="B42" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>136799366</v>
       </c>
       <c r="B43" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>136799370</v>
       </c>
       <c r="B44" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>136799367</v>
       </c>
       <c r="B58" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>136799362</v>
       </c>
       <c r="B69" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>136799372</v>
       </c>
       <c r="B70" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136799374</v>
       </c>
       <c r="B79" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>136799373</v>
       </c>
       <c r="B113" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136799375</v>
       </c>
       <c r="B129" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92553</v>
+        <v>92555</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>136799365</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>136799363</v>
       </c>
       <c r="B42" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>136799366</v>
       </c>
       <c r="B43" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>136799370</v>
       </c>
       <c r="B44" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>136799367</v>
       </c>
       <c r="B58" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>136799362</v>
       </c>
       <c r="B69" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>136799372</v>
       </c>
       <c r="B70" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136799374</v>
       </c>
       <c r="B79" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>136799364</v>
       </c>
       <c r="B90" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>136799369</v>
       </c>
       <c r="B91" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137123346</v>
       </c>
       <c r="B92" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>136799373</v>
       </c>
       <c r="B113" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>136799375</v>
       </c>
       <c r="B129" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92555</v>
+        <v>92560</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92560</v>
+        <v>92572</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92572</v>
+        <v>92573</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 4056-2022 artfynd.xlsx
+++ b/artfynd/A 4056-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
         <v>137355011</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>137355010</v>
       </c>
       <c r="B45" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>137123350</v>
       </c>
       <c r="B71" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137355006</v>
       </c>
       <c r="B72" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>137355014</v>
       </c>
       <c r="B74" t="n">
-        <v>91539</v>
+        <v>91543</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>137123346</v>
       </c>
       <c r="B92" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>136799616</v>
       </c>
       <c r="B114" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>137123349</v>
       </c>
       <c r="B115" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>137355013</v>
       </c>
       <c r="B116" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>137355012</v>
       </c>
       <c r="B123" t="n">
-        <v>80600</v>
+        <v>80604</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>136799617</v>
       </c>
       <c r="B130" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>137123352</v>
       </c>
       <c r="B131" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
